--- a/results/ir/liste_instruments_recherche_20260521_transfert_mnesys.xlsx
+++ b/results/ir/liste_instruments_recherche_20260521_transfert_mnesys.xlsx
@@ -5,24 +5,24 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pichenotf\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pichenotf\Dev\rbx-bnr-data\results\ir\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$53</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="322">
   <si>
     <t>source</t>
   </si>
@@ -708,9 +708,6 @@
     <t>nouveau_ead_id</t>
   </si>
   <si>
-    <t>nouveau_titleproper</t>
-  </si>
-  <si>
     <t>nouveau_repository</t>
   </si>
   <si>
@@ -726,46 +723,271 @@
     <t>MED_DIL_BNR</t>
   </si>
   <si>
-    <t>SUPPRIMER</t>
-  </si>
-  <si>
     <t>ANALYSER (ARCHIVES)</t>
   </si>
   <si>
     <t>TRANSFERER</t>
   </si>
   <si>
-    <t>?</t>
-  </si>
-  <si>
-    <t>bn-r/ARA</t>
-  </si>
-  <si>
-    <t>bn-r/CSV</t>
-  </si>
-  <si>
-    <t>bn-r/LAI</t>
-  </si>
-  <si>
-    <t>bn-r/LAR</t>
-  </si>
-  <si>
-    <t>bn-r/MDF</t>
-  </si>
-  <si>
-    <t>bn-r/MED</t>
-  </si>
-  <si>
-    <t>bn-r/MUS</t>
-  </si>
-  <si>
-    <t>bn-r/OBS</t>
-  </si>
-  <si>
-    <t>bn-r/PAR</t>
-  </si>
-  <si>
-    <t>bn-r/VAH</t>
+    <t>NE PAS TRANSFERER</t>
+  </si>
+  <si>
+    <t>bn-r/Partenaires</t>
+  </si>
+  <si>
+    <t>bn-r/Médiathèque</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_EPH</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_FLRS</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_FOO</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_IMA</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_LET</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_MAR</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_MEU</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_MON</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_MS</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_PHD</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_PHO</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_PIA</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_PRO</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_RAD</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_CHA</t>
+  </si>
+  <si>
+    <t>FR595126101_MUS_ARC</t>
+  </si>
+  <si>
+    <t>FR595126101_MUS_EVE</t>
+  </si>
+  <si>
+    <t>FR595126101_OBS_JOU</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_PAR</t>
+  </si>
+  <si>
+    <t>FR595126101_VAH_PUB</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_EPH.xml</t>
+  </si>
+  <si>
+    <t>MED_GUI</t>
+  </si>
+  <si>
+    <t>MED_PLA</t>
+  </si>
+  <si>
+    <t>Wasquehal</t>
+  </si>
+  <si>
+    <t>Association ARA (Roubaix)</t>
+  </si>
+  <si>
+    <t>Conservatoire de Roubaix</t>
+  </si>
+  <si>
+    <t>Amis de la Lainière et du Textile</t>
+  </si>
+  <si>
+    <t>Lire à Roubaix</t>
+  </si>
+  <si>
+    <t>Manufacture des Flandres (Roubaix)</t>
+  </si>
+  <si>
+    <t>Musée La Piscine (Roubaix)</t>
+  </si>
+  <si>
+    <t>Particulier roubaisien</t>
+  </si>
+  <si>
+    <t>Observatoire urbain de Roubaix</t>
+  </si>
+  <si>
+    <t>Ville d'art et d'histoire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FR595126101_ARA_CPS </t>
+  </si>
+  <si>
+    <t>FR595126101_MED_VDM</t>
+  </si>
+  <si>
+    <t>FR595126101_CSV</t>
+  </si>
+  <si>
+    <t>FR595126101_LAI</t>
+  </si>
+  <si>
+    <t>FR595126101_LAR_PUB</t>
+  </si>
+  <si>
+    <t>FR595126101_MDF_MTX</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_GUI</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_AFF</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_CAT</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_COM</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_CP</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_DIL</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_LBI</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_PUB</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_PLA</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_PBI</t>
+  </si>
+  <si>
+    <t>FR595126101_ARA_CPS .xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_VDM.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_CSV.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_LAI.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_LAR_PUB.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MDF_MTX.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_GUI.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_AFF.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_CAT.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_COM.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_CP.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_DIL.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_FLRS.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_FOO.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_IMA.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_LBI.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_LET.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_MAR.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_MEU.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_MON.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_MS.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_PHD.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_PHO.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_PIA.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_PRO.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_PUB.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_RAD.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_PLA.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_CHA.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MUS_ARC.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MUS_EVE.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_OBS_JOU.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_PAR.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MED_PBI.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_VAH_PUB.xml</t>
   </si>
 </sst>
 </file>
@@ -1159,7 +1381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -1170,11 +1392,13 @@
     <col min="6" max="6" width="25.7109375" style="2" customWidth="1"/>
     <col min="7" max="7" width="22" style="5" customWidth="1"/>
     <col min="8" max="8" width="16.7109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="5" customWidth="1"/>
-    <col min="10" max="13" width="9.140625" style="5"/>
+    <col min="9" max="9" width="30.85546875" style="5" customWidth="1"/>
+    <col min="10" max="10" width="25.5703125" style="5" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="5" customWidth="1"/>
+    <col min="12" max="12" width="35.42578125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1206,16 +1430,13 @@
         <v>227</v>
       </c>
       <c r="K1" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="L1" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1235,10 +1456,10 @@
         <v>27</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -1258,10 +1479,10 @@
         <v>27</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -1281,10 +1502,10 @@
         <v>27</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -1304,10 +1525,10 @@
         <v>27</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -1327,10 +1548,10 @@
         <v>27</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -1350,10 +1571,10 @@
         <v>27</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
@@ -1373,10 +1594,10 @@
         <v>27</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
@@ -1396,10 +1617,10 @@
         <v>27</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
@@ -1419,10 +1640,10 @@
         <v>27</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
@@ -1442,10 +1663,10 @@
         <v>27</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -1465,10 +1686,10 @@
         <v>27</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>5</v>
       </c>
@@ -1488,10 +1709,10 @@
         <v>27</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>5</v>
       </c>
@@ -1511,13 +1732,25 @@
         <v>48</v>
       </c>
       <c r="G14" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="H14" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="H14" s="5" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I14" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>5</v>
       </c>
@@ -1537,10 +1770,10 @@
         <v>210</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>5</v>
       </c>
@@ -1560,13 +1793,25 @@
         <v>76</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>5</v>
       </c>
@@ -1586,13 +1831,25 @@
         <v>52</v>
       </c>
       <c r="G17" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="H17" s="5" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I17" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
@@ -1612,13 +1869,25 @@
         <v>57</v>
       </c>
       <c r="G18" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="H18" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="H18" s="5" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I18" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>5</v>
       </c>
@@ -1638,13 +1907,25 @@
         <v>62</v>
       </c>
       <c r="G19" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="H19" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="H19" s="5" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I19" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>5</v>
       </c>
@@ -1664,13 +1945,25 @@
         <v>67</v>
       </c>
       <c r="G20" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="H20" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="H20" s="5" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I20" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>5</v>
       </c>
@@ -1690,13 +1983,25 @@
         <v>10</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>5</v>
       </c>
@@ -1716,13 +2021,25 @@
         <v>10</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>5</v>
       </c>
@@ -1742,13 +2059,25 @@
         <v>10</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>5</v>
       </c>
@@ -1768,13 +2097,25 @@
         <v>10</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>5</v>
       </c>
@@ -1794,13 +2135,25 @@
         <v>10</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>5</v>
       </c>
@@ -1820,13 +2173,25 @@
         <v>10</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>5</v>
       </c>
@@ -1846,13 +2211,25 @@
         <v>10</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>5</v>
       </c>
@@ -1872,13 +2249,25 @@
         <v>10</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>5</v>
       </c>
@@ -1898,13 +2287,25 @@
         <v>10</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>5</v>
       </c>
@@ -1924,13 +2325,25 @@
         <v>10</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>5</v>
       </c>
@@ -1950,10 +2363,10 @@
         <v>10</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>5</v>
       </c>
@@ -1973,13 +2386,25 @@
         <v>10</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>5</v>
       </c>
@@ -1999,13 +2424,25 @@
         <v>10</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>5</v>
       </c>
@@ -2025,13 +2462,25 @@
         <v>10</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H34" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="J34" s="5" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K34" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>5</v>
       </c>
@@ -2051,13 +2500,25 @@
         <v>10</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>5</v>
       </c>
@@ -2077,13 +2538,25 @@
         <v>10</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="L36" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>5</v>
       </c>
@@ -2103,13 +2576,25 @@
         <v>10</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="L37" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>5</v>
       </c>
@@ -2129,13 +2614,25 @@
         <v>10</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="L38" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>5</v>
       </c>
@@ -2155,13 +2652,25 @@
         <v>10</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L39" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>5</v>
       </c>
@@ -2181,13 +2690,25 @@
         <v>10</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L40" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>5</v>
       </c>
@@ -2207,10 +2728,10 @@
         <v>10</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>5</v>
       </c>
@@ -2230,13 +2751,25 @@
         <v>10</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="L42" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>5</v>
       </c>
@@ -2256,13 +2789,25 @@
         <v>10</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>5</v>
       </c>
@@ -2282,13 +2827,25 @@
         <v>10</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="L44" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>5</v>
       </c>
@@ -2308,13 +2865,25 @@
         <v>10</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>5</v>
       </c>
@@ -2334,13 +2903,25 @@
         <v>130</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="L46" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>5</v>
       </c>
@@ -2360,13 +2941,25 @@
         <v>167</v>
       </c>
       <c r="G47" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="H47" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="H47" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I47" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="L47" s="5" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>5</v>
       </c>
@@ -2386,13 +2979,25 @@
         <v>167</v>
       </c>
       <c r="G48" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="H48" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="H48" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I48" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="L48" s="5" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>5</v>
       </c>
@@ -2412,13 +3017,25 @@
         <v>176</v>
       </c>
       <c r="G49" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="H49" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="H49" s="5" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I49" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="L49" s="5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>5</v>
       </c>
@@ -2438,13 +3055,25 @@
         <v>101</v>
       </c>
       <c r="G50" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="H50" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="H50" s="5" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I50" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="J50" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="L50" s="5" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>5</v>
       </c>
@@ -2464,13 +3093,25 @@
         <v>101</v>
       </c>
       <c r="G51" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="H51" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="H51" s="5" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I51" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="L51" s="5" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>5</v>
       </c>
@@ -2490,34 +3131,49 @@
         <v>181</v>
       </c>
       <c r="G52" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="H52" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="H52" s="5" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I52" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="L52" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="B53" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M53"/>
+  <autoFilter ref="A1:L53"/>
   <sortState ref="A2:G52">
     <sortCondition ref="F2:F52"/>
     <sortCondition ref="E2:E52"/>

--- a/results/ir/liste_instruments_recherche_20260521_transfert_mnesys.xlsx
+++ b/results/ir/liste_instruments_recherche_20260521_transfert_mnesys.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="328">
   <si>
     <t>source</t>
   </si>
@@ -988,6 +988,24 @@
   </si>
   <si>
     <t>FR595126101_VAH_PUB.xml</t>
+  </si>
+  <si>
+    <t>FR595129901_MUS_02</t>
+  </si>
+  <si>
+    <t>FR595129901_MUS_02.xml</t>
+  </si>
+  <si>
+    <t>Parfumerie et savonnerie Vaissier</t>
+  </si>
+  <si>
+    <t>MUS_VAI</t>
+  </si>
+  <si>
+    <t>FR595126101_MUS_VAI.xml</t>
+  </si>
+  <si>
+    <t>FR595126101_MUS_VAI</t>
   </si>
 </sst>
 </file>
@@ -1381,7 +1399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -3172,6 +3190,44 @@
         <v>235</v>
       </c>
     </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="H54" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="K54" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="L54" s="5" t="s">
+        <v>267</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L53"/>
   <sortState ref="A2:G52">
